--- a/data/merged/2026-10-08/MERGED_IT_Wet-Dry-Floor-Washer_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_IT_Wet-Dry-Floor-Washer_2026-10-08.xlsx
@@ -882,50 +882,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Product 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR4"/>
+  <dimension ref="A1:BR3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -1902,40 +1858,40 @@
       <c r="B3" s="13"/>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>B0G66L48KD</t>
+          <t>B0G7GJZ7WQ</t>
         </is>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>JONR</t>
         </is>
       </c>
       <c r="G3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/BoschDIY/page/C0E50987-D148-4E3F-80C4-79212A89392F?lp_asin=B0G66L48KD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>Bosch Aspiratore solidi-liquidi PAS20-220P (Tubi di prolunga, tubo di aspirazione 2,2 m, tubo a gomito/impugnatura, bocchette</t>
+          <t>JONR 20000 Pa H2 aspirapolvere a secco bagnato,Design Innovativo Protezione Odori,Serbatoio Acqua Extra Grande 1500ml con Pos</t>
         </is>
       </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0G66L48KD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/416etd8+eUL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31y8P58cu8L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>B0G66L48KD</t>
+          <t>B0G7GJZ7WQ</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
@@ -1949,7 +1905,7 @@
         </is>
       </c>
       <c r="O3" s="15">
-        <v>31790</v>
+        <v>912273</v>
       </c>
       <c r="P3"/>
       <c r="Q3" s="16">
@@ -1958,17 +1914,17 @@
       <c r="R3" s="17" t="inlineStr">
         <is>
           <t>Aspiratori solidi-liquidi per uso domestico
-Ugelli
 Torna ai risultati
-Aspiratori liquidi-solidi</t>
+Aspiratori liquidi-solidi
+Aspirapolvere verticale</t>
         </is>
       </c>
       <c r="S3" s="18" t="inlineStr">
         <is>
-          <t>2
-1
-17333
-47</t>
+          <t>3
+409491
+435
+145</t>
         </is>
       </c>
       <c r="T3" s="15"/>
@@ -1977,22 +1933,22 @@
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
       <c r="Y3" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="20">
-        <v>147.46</v>
+        <v>298.41</v>
       </c>
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="19">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AE3" s="15">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AF3" s="21">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG3" s="22">
         <v>0</v>
@@ -2004,15 +1960,15 @@
       <c r="AJ3"/>
       <c r="AK3" s="13" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AL3" s="19">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="AM3" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN3" s="13"/>
@@ -2020,7 +1976,7 @@
       <c r="AP3"/>
       <c r="AQ3" s="19"/>
       <c r="AR3" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS3" s="14" t="inlineStr">
         <is>
@@ -2029,18 +1985,14 @@
       </c>
       <c r="AT3" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU3" s="13"/>
       <c r="AV3" s="14"/>
       <c r="AW3" s="13"/>
       <c r="AX3" s="13"/>
-      <c r="AY3" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY3" s="13"/>
       <c r="AZ3" s="13"/>
       <c r="BA3" s="13"/>
       <c r="BB3" s="13"/>
@@ -2054,20 +2006,16 @@
       <c r="BF3" s="13"/>
       <c r="BG3" s="13"/>
       <c r="BH3" s="14"/>
-      <c r="BI3" s="23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BI3" s="23"/>
       <c r="BJ3" s="23" t="inlineStr">
         <is>
-          <t>6 Chilogrammi</t>
+          <t>3,5 Chilogrammi</t>
         </is>
       </c>
       <c r="BK3" s="23"/>
       <c r="BL3" s="23" t="inlineStr">
         <is>
-          <t>37,6L x 36,5l x 49,2H cm</t>
+          <t>27L x 21l x 110H cm</t>
         </is>
       </c>
       <c r="BM3" s="23"/>
@@ -2076,180 +2024,6 @@
       <c r="BP3"/>
       <c r="BQ3" s="23"/>
       <c r="BR3"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>B0G7GJZ7WQ</t>
-        </is>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>JONR</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>JONR 20000 Pa H2 aspirapolvere a secco bagnato,Design Innovativo Protezione Odori,Serbatoio Acqua Extra Grande 1500ml con Pos</t>
-        </is>
-      </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1</t>
-        </is>
-      </c>
-      <c r="K4" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31y8P58cu8L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
-        <is>
-          <t>B0G7GJZ7WQ</t>
-        </is>
-      </c>
-      <c r="M4" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspiratori solidi-liquidi per uso domestico</t>
-        </is>
-      </c>
-      <c r="N4" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e cucina</t>
-        </is>
-      </c>
-      <c r="O4" s="15">
-        <v>912273</v>
-      </c>
-      <c r="P4"/>
-      <c r="Q4" s="16">
-        <v>0</v>
-      </c>
-      <c r="R4" s="17" t="inlineStr">
-        <is>
-          <t>Aspiratori solidi-liquidi per uso domestico
-Torna ai risultati
-Aspiratori liquidi-solidi
-Aspirapolvere verticale</t>
-        </is>
-      </c>
-      <c r="S4" s="18" t="inlineStr">
-        <is>
-          <t>3
-409491
-435
-145</t>
-        </is>
-      </c>
-      <c r="T4" s="15"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="15"/>
-      <c r="Y4" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="20">
-        <v>298.41</v>
-      </c>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="19">
-        <v>49</v>
-      </c>
-      <c r="AE4" s="15">
-        <v>-2</v>
-      </c>
-      <c r="AF4" s="21">
-        <v>3.5</v>
-      </c>
-      <c r="AG4" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH4"/>
-      <c r="AI4" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ4"/>
-      <c r="AK4" s="13" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="AL4" s="19">
-        <v>243</v>
-      </c>
-      <c r="AM4" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN4" s="13"/>
-      <c r="AO4" s="13"/>
-      <c r="AP4"/>
-      <c r="AQ4" s="19"/>
-      <c r="AR4" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS4" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT4" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="14"/>
-      <c r="AW4" s="13"/>
-      <c r="AX4" s="13"/>
-      <c r="AY4" s="13"/>
-      <c r="AZ4" s="13"/>
-      <c r="BA4" s="13"/>
-      <c r="BB4" s="13"/>
-      <c r="BC4" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD4" s="13"/>
-      <c r="BE4" s="13"/>
-      <c r="BF4" s="13"/>
-      <c r="BG4" s="13"/>
-      <c r="BH4" s="14"/>
-      <c r="BI4" s="23"/>
-      <c r="BJ4" s="23" t="inlineStr">
-        <is>
-          <t>3,5 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK4" s="23"/>
-      <c r="BL4" s="23" t="inlineStr">
-        <is>
-          <t>27L x 21l x 110H cm</t>
-        </is>
-      </c>
-      <c r="BM4" s="23"/>
-      <c r="BN4"/>
-      <c r="BO4" s="23"/>
-      <c r="BP4"/>
-      <c r="BQ4" s="23"/>
-      <c r="BR4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2262,28 +2036,21 @@
     <hyperlink ref="L2" r:id="rId5" tooltip="https://www.amazon.it/dp/B0FN46V7CN"/>
     <hyperlink ref="M2" r:id="rId6" tooltip="https://www.amazon.it/b?node=218944968031"/>
     <hyperlink ref="N2" r:id="rId7"/>
-    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.it/dp/B0G66L48KD"/>
-    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.it/stores/BoschDIY/page/C0E50987-D148-4E3F-80C4-79212A89392F?lp_asin=B0G66L48KD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.it/dp/B0G66L48KD?psc=1"/>
-    <hyperlink ref="K3" r:id="rId11" tooltip="https://m.media-amazon.com/images/I/416etd8+eUL._AC_US600_.jpg"/>
-    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.it/dp/B0G66L48KD"/>
+    <hyperlink ref="C3" r:id="rId8" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
+    <hyperlink ref="G3" r:id="rId9" tooltip="https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J3" r:id="rId10" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1"/>
+    <hyperlink ref="K3" r:id="rId11" tooltip="https://m.media-amazon.com/images/I/31y8P58cu8L._AC_US600_.jpg"/>
+    <hyperlink ref="L3" r:id="rId12" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
     <hyperlink ref="M3" r:id="rId13" tooltip="https://www.amazon.it/b?node=218944968031"/>
     <hyperlink ref="N3" r:id="rId14"/>
-    <hyperlink ref="C4" r:id="rId15" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="G4" r:id="rId16" tooltip="https://www.amazon.it/stores/JONR/page/23282C74-A95B-4A91-97BF-B8CE072F6B75?lp_asin=B0G7GJZ7WQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J4" r:id="rId17" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ?psc=1"/>
-    <hyperlink ref="K4" r:id="rId18" tooltip="https://m.media-amazon.com/images/I/31y8P58cu8L._AC_US600_.jpg"/>
-    <hyperlink ref="L4" r:id="rId19" tooltip="https://www.amazon.it/dp/B0G7GJZ7WQ"/>
-    <hyperlink ref="M4" r:id="rId20" tooltip="https://www.amazon.it/b?node=218944968031"/>
-    <hyperlink ref="N4" r:id="rId21"/>
   </hyperlinks>
-  <drawing r:id="rId22"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -2353,7 +2120,7 @@
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>JONR</t>
         </is>
       </c>
       <c r="B3" s="15">
@@ -2366,25 +2133,6 @@
       <c r="E3" s="15"/>
       <c r="F3" s="20"/>
       <c r="G3" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>JONR</t>
-        </is>
-      </c>
-      <c r="B4" s="15">
-        <v>0</v>
-      </c>
-      <c r="C4" s="15">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="22">
         <v>0.0</v>
       </c>
     </row>
